--- a/Code/Jupiter/Connect4/Eval summary.xlsx
+++ b/Code/Jupiter/Connect4/Eval summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R189"/>
+  <dimension ref="A1:R211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11179,8 +11179,1152 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_1.pt</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>1218.744448240556</v>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>0.4713311150277231</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K190" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L190" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M190" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N190" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O190" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P190" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>PPO_847.pt</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>1220.381604291979</v>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>0.4474700949026029</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K191" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L191" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M191" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N191" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O191" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P191" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>PPO_848.pt</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>1216.735305791291</v>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>0.4552802128381769</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K192" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L192" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M192" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N192" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O192" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P192" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_2.pt</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>1190.996731223537</v>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>0.452406099159321</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H193" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M193" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N193" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O193" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P193" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_3.pt</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>1190.46096559351</v>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>0.4555852315741751</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H194" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K194" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L194" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M194" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N194" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O194" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P194" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_4.pt</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>1212.052456761498</v>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>0.4583107125265415</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H195" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K195" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M195" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N195" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O195" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P195" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>PPO_915.pt</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>1188.984752857169</v>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>0.2735611550491202</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J196" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K196" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L196" s="3" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="M196" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N196" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O196" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P196" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>PPO_S1.pt</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>1212.047578617151</v>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>0.4560649692769165</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H197" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K197" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L197" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M197" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N197" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O197" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P197" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_5.pt</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>1237.856430117117</v>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>0.4670786529110676</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K198" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L198" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M198" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N198" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O198" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P198" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_6.pt</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>1237.856430117117</v>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>0.4670786529110676</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H199" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K199" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L199" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M199" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N199" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O199" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P199" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_7.pt</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>1191.190274173785</v>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>0.4527700995187827</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J200" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K200" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M200" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N200" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O200" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P200" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>PPO_S2.pt</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n">
+        <v>1172.063833333255</v>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>0.4411761236478068</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K201" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M201" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O201" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P201" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>PPO_849.pt</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>1267.272510511526</v>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>0.470325189643384</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I202" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K202" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L202" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M202" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N202" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O202" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P202" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>SOUP_9.pt</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>1149.58550612215</v>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>0.2603910301897644</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K203" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L203" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M203" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N203" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O203" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P203" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>PPO_850.pt</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>1185.922536146838</v>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>0.424653908636354</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K204" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L204" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M204" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N204" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O204" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P204" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>PPO_916.pt</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>1251.428502330562</v>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>0.3129186623541395</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H205" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J205" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K205" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L205" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M205" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N205" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O205" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P205" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>PPO_917.pt</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>1248.623324285968</v>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>0.3073740598990646</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H206" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J206" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K206" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L206" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M206" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N206" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O206" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P206" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>X_1.pt</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>1226.704969819507</v>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>0.4601657578367173</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H207" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K207" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L207" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M207" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N207" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O207" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P207" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>PPO_918.pt</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>1236.045284561189</v>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>0.3090288768233485</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K208" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L208" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M208" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N208" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O208" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P208" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>PPO_919.pt</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>1216.231693646245</v>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>0.2761121499467415</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H209" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K209" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M209" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N209" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O209" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P209" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>PPO_851.pt</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>1165.903223687206</v>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>0.461820167957455</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K210" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L210" s="3" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="M210" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N210" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O210" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P210" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>PPO_852X.pt</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>1195.016816856797</v>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>0.4585094781257273</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H211" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I211" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K211" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L211" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M211" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N211" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O211" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P211" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R189"/>
+  <autoFilter ref="A1:R211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Eval summary.xlsx
+++ b/Code/Jupiter/Connect4/Eval summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$213</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R211"/>
+  <dimension ref="A1:R213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12323,8 +12323,112 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>PPO_920.pt</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>1163.038533838413</v>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>0.2621292081307328</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K212" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L212" s="3" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="M212" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N212" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P212" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>PPO_853.pt</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>1180.65001090702</v>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>0.4202328055985288</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K213" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L213" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M213" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N213" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O213" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P213" s="3" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R211"/>
+  <autoFilter ref="A1:R213"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Eval summary.xlsx
+++ b/Code/Jupiter/Connect4/Eval summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R213"/>
+  <dimension ref="A1:R215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12427,8 +12427,112 @@
         <v>0.35</v>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>PPO_853.pt</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="n">
+        <v>1180.65001090702</v>
+      </c>
+      <c r="C214" s="3" t="n">
+        <v>0.4202328055985288</v>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K214" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L214" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M214" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N214" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O214" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P214" s="3" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>PPO_921.pt</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>1176.938388635525</v>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>0.2917819489508929</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H215" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I215" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K215" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L215" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M215" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N215" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O215" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P215" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R213"/>
+  <autoFilter ref="A1:R215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Eval summary.xlsx
+++ b/Code/Jupiter/Connect4/Eval summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R215"/>
+  <dimension ref="A1:R234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12531,8 +12531,996 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>PPO_922.pt</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>1097.834519527536</v>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>0.2688092221795766</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K216" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L216" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M216" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O216" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P216" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>PPO_923.pt</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>1076.781501411108</v>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>0.2825950299662746</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J217" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K217" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L217" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M217" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N217" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O217" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P217" s="3" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>PPO_924.pt</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>1145.391574609841</v>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>0.3215862023011279</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I218" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J218" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K218" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L218" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M218" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N218" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O218" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P218" s="3" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>PPO_854.pt</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>1211.926838531002</v>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>0.4506474845530693</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I219" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J219" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K219" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L219" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M219" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N219" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O219" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P219" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>PPO_855.pt</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>1168.291290468531</v>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>0.4451620150809767</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J220" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K220" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L220" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M220" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N220" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O220" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P220" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>PPO_856.pt</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>1188.456452092554</v>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>0.4331214025109114</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J221" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K221" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L221" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M221" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N221" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O221" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P221" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>BASE_10.pt</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>1215.754173892849</v>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>0.2119001492870971</v>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I222" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J222" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K222" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L222" s="3" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="M222" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N222" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O222" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P222" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>PPO_857.pt</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>1094.186196309048</v>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>0.3264674375177399</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J223" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K223" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L223" s="3" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="M223" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N223" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O223" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P223" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>PPO_858.pt</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>1142.148887390922</v>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>0.4433330916139375</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I224" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J224" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K224" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L224" s="3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M224" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N224" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O224" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P224" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1001.pt</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>1334.951833846339</v>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>0.4763387356501952</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H225" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I225" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J225" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K225" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L225" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M225" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N225" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O225" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P225" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1002.pt</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>1335.019040449412</v>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>0.4270344419361761</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H226" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I226" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J226" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K226" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L226" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M226" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N226" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O226" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P226" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1003.pt</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>1313.182888493477</v>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>0.3944334087621894</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J227" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K227" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L227" s="3" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="M227" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N227" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O227" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P227" s="3" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1004.pt</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>1367.670305082837</v>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>0.5242786740757235</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I228" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J228" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K228" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L228" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M228" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N228" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O228" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P228" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>PPO_859.pt</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>1161.87048100682</v>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>0.4123907221672718</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G229" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H229" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I229" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J229" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K229" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L229" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="M229" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N229" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O229" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P229" s="3" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1005.pt</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>1287.815379931434</v>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>0.3458693378787646</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I230" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J230" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K230" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L230" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M230" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N230" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O230" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P230" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>PPO_925.pt</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>1107.500214061666</v>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>0.2845280800441681</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J231" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K231" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L231" s="3" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="M231" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N231" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O231" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P231" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>BASE_11a.pt</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>1227.076711817355</v>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>0.187169392531011</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H232" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I232" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J232" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K232" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="M232" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N232" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O232" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P232" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1101.pt</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>1245.694189333076</v>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>0.3135622136864409</v>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H233" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I233" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J233" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K233" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L233" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M233" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N233" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O233" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P233" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>PPO_926.pt</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>1109.295153858635</v>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>0.3069972663399826</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I234" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J234" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K234" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L234" s="3" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="M234" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N234" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O234" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P234" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R215"/>
+  <autoFilter ref="A1:R234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Eval summary.xlsx
+++ b/Code/Jupiter/Connect4/Eval summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$R$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R234"/>
+  <dimension ref="A1:R248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13519,8 +13519,736 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1006.pt</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>1206.65130484654</v>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>0.3349433408540392</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I235" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J235" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K235" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L235" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M235" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N235" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O235" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P235" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1007.pt</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>1217.731277378666</v>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>0.3140398530117269</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H236" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I236" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J236" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K236" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M236" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N236" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O236" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P236" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1008.pt</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>1250.657111716167</v>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>0.3148282698122769</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G237" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I237" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J237" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K237" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L237" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M237" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N237" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O237" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P237" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1009.pt</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>1269.896883639238</v>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>0.3676758662680099</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I238" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J238" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K238" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L238" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M238" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N238" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O238" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P238" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1010.pt</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>1262.219429885698</v>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>0.361002166606684</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J239" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K239" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L239" s="3" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="M239" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N239" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O239" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P239" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>PPO_1011.pt</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>1244.496461926162</v>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>0.3262456354537212</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I240" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J240" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K240" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M240" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N240" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O240" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P240" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>AZ_003.pt</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>1376.101520329182</v>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>0.5337262026266172</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I241" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J241" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K241" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L241" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M241" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N241" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O241" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P241" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>AZ_005.pt</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>1379.874831512289</v>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>0.5401215264610383</v>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J242" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K242" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L242" s="3" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M242" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N242" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O242" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P242" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>AZ_926.pt</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>1111.047812336767</v>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>0.2701274914927058</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G243" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I243" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J243" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K243" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L243" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M243" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N243" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O243" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P243" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>PPO_2001.pt</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>1354.375858386892</v>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>0.5624862278332159</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I244" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J244" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K244" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L244" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M244" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N244" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O244" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P244" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>AZ_006.pt</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>1244.49235524638</v>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>0.3229308097338512</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I245" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J245" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K245" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L245" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M245" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N245" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O245" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P245" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>PPO_2002.pt</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>1329.1464926691</v>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>0.5625881643709988</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I246" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J246" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K246" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L246" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M246" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N246" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O246" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P246" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>PPO_2003.pt</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>1337.197941718542</v>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>0.5086188036388262</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J247" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K247" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L247" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M247" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N247" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O247" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P247" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>PPO_2004.pt</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>1316.051530461457</v>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>0.4959842055617689</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I248" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K248" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L248" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M248" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N248" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O248" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P248" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R234"/>
+  <autoFilter ref="A1:R248"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>